--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-flow-feature-wf169.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-flow-feature-wf169.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/StructureDefinition/ti-flow-feature-wf169</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/ti-flow-feature-wf169</t>
   </si>
   <si>
     <t>Version</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/StructureDefinition/ti-feature-definition</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/ti-feature-definition</t>
   </si>
   <si>
     <t>Abstract</t>
